--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T10:14:31+00:00</t>
+    <t>2026-07-08T15:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T15:46:54+00:00</t>
+    <t>2026-07-09T09:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:13:13+00:00</t>
+    <t>2026-07-10T12:01:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:01:50+00:00</t>
+    <t>2026-07-10T12:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:28:44+00:00</t>
+    <t>2026-07-10T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:58:40+00:00</t>
+    <t>2026-07-20T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:08:41+00:00</t>
+    <t>2026-07-21T09:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:08:11+00:00</t>
+    <t>2026-07-21T09:10:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:10:59+00:00</t>
+    <t>2026-07-22T09:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:27:19+00:00</t>
+    <t>2026-07-28T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T07:28:06+00:00</t>
+    <t>2026-07-30T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:11:50+00:00</t>
+    <t>2026-08-03T07:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T07:00:21+00:00</t>
+    <t>2026-08-04T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:50:37+00:00</t>
+    <t>2026-08-04T08:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:17:33+00:00</t>
+    <t>2026-08-06T12:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:56:12+00:00</t>
+    <t>2026-08-07T08:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:15:28+00:00</t>
+    <t>2026-08-07T09:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -23980,7 +23980,7 @@
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G180" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$262</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$263</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9670" uniqueCount="886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9708" uniqueCount="892">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:41:31+00:00</t>
+    <t>2026-08-07T12:53:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2574,6 +2574,25 @@
   </si>
   <si>
     <t>Change Made</t>
+  </si>
+  <si>
+    <t>Composition.section.extension:section-note</t>
+  </si>
+  <si>
+    <t>section-note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {note|5.3.0}
+</t>
+  </si>
+  <si>
+    <t>Commentaires supplémentaires pour chaque section.</t>
+  </si>
+  <si>
+    <t>Permet de porter des commentaires dans chaque section.</t>
+  </si>
+  <si>
+    <t>This extension SHALL NOT be used if the resource already has standard 'note' element (or equivalent) of type Annotation on the same element</t>
   </si>
   <si>
     <t>Composition.section.modifierExtension</t>
@@ -3087,7 +3106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO262"/>
+  <dimension ref="A1:AO263"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="67.234375" customWidth="true" bestFit="true"/>
@@ -32372,11 +32391,13 @@
         <v>822</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="C252" s="2"/>
+        <v>819</v>
+      </c>
+      <c r="C252" t="s" s="2">
+        <v>823</v>
+      </c>
       <c r="D252" t="s" s="2">
-        <v>581</v>
+        <v>78</v>
       </c>
       <c r="E252" s="2"/>
       <c r="F252" t="s" s="2">
@@ -32389,26 +32410,24 @@
         <v>78</v>
       </c>
       <c r="I252" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J252" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>112</v>
+        <v>824</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>582</v>
+        <v>825</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>583</v>
+        <v>826</v>
       </c>
       <c r="N252" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O252" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>827</v>
+      </c>
+      <c r="O252" s="2"/>
       <c r="P252" t="s" s="2">
         <v>78</v>
       </c>
@@ -32456,7 +32475,7 @@
         <v>78</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>584</v>
+        <v>119</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>79</v>
@@ -32474,7 +32493,7 @@
         <v>78</v>
       </c>
       <c r="AL252" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="AM252" t="s" s="2">
         <v>78</v>
@@ -32486,47 +32505,47 @@
         <v>78</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
-        <v>824</v>
+        <v>581</v>
       </c>
       <c r="E253" s="2"/>
       <c r="F253" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G253" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H253" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I253" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I253" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J253" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>825</v>
+        <v>582</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>826</v>
+        <v>583</v>
       </c>
       <c r="N253" t="s" s="2">
-        <v>827</v>
+        <v>115</v>
       </c>
       <c r="O253" t="s" s="2">
-        <v>828</v>
+        <v>413</v>
       </c>
       <c r="P253" t="s" s="2">
         <v>78</v>
@@ -32575,28 +32594,28 @@
         <v>78</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>823</v>
+        <v>584</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH253" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI253" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ253" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK253" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL253" t="s" s="2">
-        <v>556</v>
+        <v>196</v>
       </c>
       <c r="AM253" t="s" s="2">
-        <v>557</v>
+        <v>78</v>
       </c>
       <c r="AN253" t="s" s="2">
         <v>78</v>
@@ -32614,11 +32633,11 @@
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
-        <v>78</v>
+        <v>830</v>
       </c>
       <c r="E254" s="2"/>
       <c r="F254" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G254" t="s" s="2">
         <v>91</v>
@@ -32633,19 +32652,19 @@
         <v>78</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>236</v>
+        <v>105</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="N254" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="O254" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="P254" t="s" s="2">
         <v>78</v>
@@ -32670,11 +32689,13 @@
         <v>78</v>
       </c>
       <c r="X254" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="Y254" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y254" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z254" t="s" s="2">
-        <v>834</v>
+        <v>78</v>
       </c>
       <c r="AA254" t="s" s="2">
         <v>78</v>
@@ -32710,10 +32731,10 @@
         <v>78</v>
       </c>
       <c r="AL254" t="s" s="2">
-        <v>457</v>
+        <v>556</v>
       </c>
       <c r="AM254" t="s" s="2">
-        <v>458</v>
+        <v>557</v>
       </c>
       <c r="AN254" t="s" s="2">
         <v>78</v>
@@ -32722,7 +32743,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="255" hidden="true">
+    <row r="255">
       <c r="A255" t="s" s="2">
         <v>835</v>
       </c>
@@ -32735,13 +32756,13 @@
       </c>
       <c r="E255" s="2"/>
       <c r="F255" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G255" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H255" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I255" t="s" s="2">
         <v>78</v>
@@ -32750,17 +32771,19 @@
         <v>78</v>
       </c>
       <c r="K255" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L255" t="s" s="2">
         <v>836</v>
       </c>
-      <c r="L255" t="s" s="2">
+      <c r="M255" t="s" s="2">
         <v>837</v>
       </c>
-      <c r="M255" t="s" s="2">
+      <c r="N255" t="s" s="2">
         <v>838</v>
       </c>
-      <c r="N255" s="2"/>
       <c r="O255" t="s" s="2">
-        <v>536</v>
+        <v>839</v>
       </c>
       <c r="P255" t="s" s="2">
         <v>78</v>
@@ -32785,13 +32808,11 @@
         <v>78</v>
       </c>
       <c r="X255" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y255" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="Y255" s="2"/>
       <c r="Z255" t="s" s="2">
-        <v>78</v>
+        <v>840</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>78</v>
@@ -32815,7 +32836,7 @@
         <v>79</v>
       </c>
       <c r="AH255" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI255" t="s" s="2">
         <v>78</v>
@@ -32827,24 +32848,24 @@
         <v>78</v>
       </c>
       <c r="AL255" t="s" s="2">
-        <v>538</v>
+        <v>457</v>
       </c>
       <c r="AM255" t="s" s="2">
-        <v>539</v>
+        <v>458</v>
       </c>
       <c r="AN255" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO255" t="s" s="2">
-        <v>541</v>
+        <v>78</v>
       </c>
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -32855,7 +32876,7 @@
         <v>79</v>
       </c>
       <c r="G256" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H256" t="s" s="2">
         <v>78</v>
@@ -32867,18 +32888,18 @@
         <v>78</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>797</v>
+        <v>842</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="N256" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="O256" s="2"/>
+        <v>844</v>
+      </c>
+      <c r="N256" s="2"/>
+      <c r="O256" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="P256" t="s" s="2">
         <v>78</v>
       </c>
@@ -32926,13 +32947,13 @@
         <v>78</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH256" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI256" t="s" s="2">
         <v>78</v>
@@ -32944,24 +32965,24 @@
         <v>78</v>
       </c>
       <c r="AL256" t="s" s="2">
-        <v>78</v>
+        <v>538</v>
       </c>
       <c r="AM256" t="s" s="2">
-        <v>843</v>
+        <v>539</v>
       </c>
       <c r="AN256" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO256" t="s" s="2">
-        <v>78</v>
+        <v>541</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -32969,13 +32990,13 @@
       </c>
       <c r="E257" s="2"/>
       <c r="F257" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G257" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H257" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I257" t="s" s="2">
         <v>78</v>
@@ -32984,16 +33005,16 @@
         <v>78</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>183</v>
+        <v>797</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="O257" s="2"/>
       <c r="P257" t="s" s="2">
@@ -33043,7 +33064,7 @@
         <v>78</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>79</v>
@@ -33052,7 +33073,7 @@
         <v>91</v>
       </c>
       <c r="AI257" t="s" s="2">
-        <v>848</v>
+        <v>78</v>
       </c>
       <c r="AJ257" t="s" s="2">
         <v>103</v>
@@ -33061,7 +33082,7 @@
         <v>78</v>
       </c>
       <c r="AL257" t="s" s="2">
-        <v>849</v>
+        <v>78</v>
       </c>
       <c r="AM257" t="s" s="2">
         <v>849</v>
@@ -33073,7 +33094,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="258" hidden="true">
+    <row r="258">
       <c r="A258" t="s" s="2">
         <v>850</v>
       </c>
@@ -33086,13 +33107,13 @@
       </c>
       <c r="E258" s="2"/>
       <c r="F258" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G258" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H258" t="s" s="2">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I258" t="s" s="2">
         <v>78</v>
@@ -33101,7 +33122,7 @@
         <v>78</v>
       </c>
       <c r="K258" t="s" s="2">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="L258" t="s" s="2">
         <v>851</v>
@@ -33112,9 +33133,7 @@
       <c r="N258" t="s" s="2">
         <v>853</v>
       </c>
-      <c r="O258" t="s" s="2">
-        <v>854</v>
-      </c>
+      <c r="O258" s="2"/>
       <c r="P258" t="s" s="2">
         <v>78</v>
       </c>
@@ -33138,13 +33157,13 @@
         <v>78</v>
       </c>
       <c r="X258" t="s" s="2">
-        <v>326</v>
+        <v>78</v>
       </c>
       <c r="Y258" t="s" s="2">
-        <v>855</v>
+        <v>78</v>
       </c>
       <c r="Z258" t="s" s="2">
-        <v>856</v>
+        <v>78</v>
       </c>
       <c r="AA258" t="s" s="2">
         <v>78</v>
@@ -33171,7 +33190,7 @@
         <v>91</v>
       </c>
       <c r="AI258" t="s" s="2">
-        <v>78</v>
+        <v>854</v>
       </c>
       <c r="AJ258" t="s" s="2">
         <v>103</v>
@@ -33180,24 +33199,24 @@
         <v>78</v>
       </c>
       <c r="AL258" t="s" s="2">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="AM258" t="s" s="2">
-        <v>109</v>
+        <v>855</v>
       </c>
       <c r="AN258" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO258" t="s" s="2">
-        <v>460</v>
+        <v>78</v>
       </c>
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33220,19 +33239,19 @@
         <v>78</v>
       </c>
       <c r="K259" t="s" s="2">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="L259" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="M259" t="s" s="2">
+        <v>858</v>
+      </c>
+      <c r="N259" t="s" s="2">
         <v>859</v>
       </c>
-      <c r="M259" t="s" s="2">
+      <c r="O259" t="s" s="2">
         <v>860</v>
-      </c>
-      <c r="N259" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="O259" t="s" s="2">
-        <v>862</v>
       </c>
       <c r="P259" t="s" s="2">
         <v>78</v>
@@ -33257,13 +33276,13 @@
         <v>78</v>
       </c>
       <c r="X259" t="s" s="2">
-        <v>176</v>
+        <v>326</v>
       </c>
       <c r="Y259" t="s" s="2">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="Z259" t="s" s="2">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="AA259" t="s" s="2">
         <v>78</v>
@@ -33281,7 +33300,7 @@
         <v>78</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>79</v>
@@ -33299,7 +33318,7 @@
         <v>78</v>
       </c>
       <c r="AL259" t="s" s="2">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="AM259" t="s" s="2">
         <v>109</v>
@@ -33308,15 +33327,15 @@
         <v>78</v>
       </c>
       <c r="AO259" t="s" s="2">
-        <v>78</v>
+        <v>460</v>
       </c>
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33327,7 +33346,7 @@
         <v>79</v>
       </c>
       <c r="G260" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H260" t="s" s="2">
         <v>78</v>
@@ -33339,18 +33358,20 @@
         <v>78</v>
       </c>
       <c r="K260" t="s" s="2">
-        <v>797</v>
+        <v>236</v>
       </c>
       <c r="L260" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="M260" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="N260" t="s" s="2">
         <v>867</v>
       </c>
-      <c r="M260" t="s" s="2">
+      <c r="O260" t="s" s="2">
         <v>868</v>
       </c>
-      <c r="N260" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="O260" s="2"/>
       <c r="P260" t="s" s="2">
         <v>78</v>
       </c>
@@ -33374,13 +33395,13 @@
         <v>78</v>
       </c>
       <c r="X260" t="s" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="Y260" t="s" s="2">
-        <v>78</v>
+        <v>869</v>
       </c>
       <c r="Z260" t="s" s="2">
-        <v>78</v>
+        <v>870</v>
       </c>
       <c r="AA260" t="s" s="2">
         <v>78</v>
@@ -33398,16 +33419,16 @@
         <v>78</v>
       </c>
       <c r="AF260" t="s" s="2">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="AG260" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH260" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI260" t="s" s="2">
-        <v>870</v>
+        <v>78</v>
       </c>
       <c r="AJ260" t="s" s="2">
         <v>103</v>
@@ -33419,7 +33440,7 @@
         <v>871</v>
       </c>
       <c r="AM260" t="s" s="2">
-        <v>872</v>
+        <v>109</v>
       </c>
       <c r="AN260" t="s" s="2">
         <v>78</v>
@@ -33430,10 +33451,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33444,7 +33465,7 @@
         <v>79</v>
       </c>
       <c r="G261" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H261" t="s" s="2">
         <v>78</v>
@@ -33456,20 +33477,18 @@
         <v>78</v>
       </c>
       <c r="K261" t="s" s="2">
-        <v>236</v>
+        <v>797</v>
       </c>
       <c r="L261" t="s" s="2">
+        <v>873</v>
+      </c>
+      <c r="M261" t="s" s="2">
         <v>874</v>
       </c>
-      <c r="M261" t="s" s="2">
+      <c r="N261" t="s" s="2">
         <v>875</v>
       </c>
-      <c r="N261" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="O261" t="s" s="2">
-        <v>877</v>
-      </c>
+      <c r="O261" s="2"/>
       <c r="P261" t="s" s="2">
         <v>78</v>
       </c>
@@ -33493,13 +33512,13 @@
         <v>78</v>
       </c>
       <c r="X261" t="s" s="2">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="Y261" t="s" s="2">
-        <v>878</v>
+        <v>78</v>
       </c>
       <c r="Z261" t="s" s="2">
-        <v>879</v>
+        <v>78</v>
       </c>
       <c r="AA261" t="s" s="2">
         <v>78</v>
@@ -33517,16 +33536,16 @@
         <v>78</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH261" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AI261" t="s" s="2">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="AJ261" t="s" s="2">
         <v>103</v>
@@ -33535,10 +33554,10 @@
         <v>78</v>
       </c>
       <c r="AL261" t="s" s="2">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AM261" t="s" s="2">
-        <v>109</v>
+        <v>878</v>
       </c>
       <c r="AN261" t="s" s="2">
         <v>78</v>
@@ -33549,10 +33568,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33563,7 +33582,7 @@
         <v>79</v>
       </c>
       <c r="G262" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H262" t="s" s="2">
         <v>78</v>
@@ -33575,18 +33594,20 @@
         <v>78</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>81</v>
+        <v>236</v>
       </c>
       <c r="L262" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="M262" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="N262" t="s" s="2">
         <v>882</v>
       </c>
-      <c r="M262" t="s" s="2">
+      <c r="O262" t="s" s="2">
         <v>883</v>
       </c>
-      <c r="N262" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="O262" s="2"/>
       <c r="P262" t="s" s="2">
         <v>78</v>
       </c>
@@ -33610,13 +33631,13 @@
         <v>78</v>
       </c>
       <c r="X262" t="s" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="Y262" t="s" s="2">
-        <v>78</v>
+        <v>884</v>
       </c>
       <c r="Z262" t="s" s="2">
-        <v>78</v>
+        <v>885</v>
       </c>
       <c r="AA262" t="s" s="2">
         <v>78</v>
@@ -33634,16 +33655,16 @@
         <v>78</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH262" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AI262" t="s" s="2">
-        <v>848</v>
+        <v>876</v>
       </c>
       <c r="AJ262" t="s" s="2">
         <v>103</v>
@@ -33652,20 +33673,137 @@
         <v>78</v>
       </c>
       <c r="AL262" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="AM262" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AN262" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO262" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="263" hidden="true">
+      <c r="A263" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="C263" s="2"/>
+      <c r="D263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E263" s="2"/>
+      <c r="F263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G263" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K263" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L263" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="M263" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="N263" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="O263" s="2"/>
+      <c r="P263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q263" s="2"/>
+      <c r="R263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF263" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="AG263" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH263" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI263" t="s" s="2">
+        <v>854</v>
+      </c>
+      <c r="AJ263" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL263" t="s" s="2">
         <v>816</v>
       </c>
-      <c r="AM262" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="AN262" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO262" t="s" s="2">
+      <c r="AM263" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="AN263" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO263" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO262">
+  <autoFilter ref="A1:AO263">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -33675,7 +33813,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI261">
+  <conditionalFormatting sqref="A2:AI262">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T12:53:43+00:00</t>
+    <t>2026-09-03T14:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1152,7 +1152,7 @@
     <t>Composition.extension:participant.extension:type.value[x]</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J144-ParticipationType-CISIS/FHIR/JDV-J144-ParticipationType-CISIS|20210326120000</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-doc-vs-participation-type-participant|0.1.0</t>
   </si>
   <si>
     <t>Composition.extension:participant.extension:function</t>
@@ -2633,7 +2633,7 @@
     <t>Provides computable standardized labels to topics within the document.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-section-document-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-section-document-cisis|20260716085852</t>
   </si>
   <si>
     <t>Composition.section.author</t>
@@ -3134,7 +3134,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="97.015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="89.12890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-fr-composition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-composition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:26:41+00:00</t>
+    <t>2026-09-04T11:53:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
